--- a/public/post/drafts/weekly-recap/2025Lillehammer/ladies_weekend.xlsx
+++ b/public/post/drafts/weekly-recap/2025Lillehammer/ladies_weekend.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
   <si>
     <t xml:space="preserve">Skier</t>
   </si>
@@ -38,334 +38,376 @@
     <t xml:space="preserve">Points Difference</t>
   </si>
   <si>
+    <t xml:space="preserve">Jessie Diggins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Victoria Carl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Therese Johaug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Norway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heidi Weng</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jonna Sundling</t>
   </si>
   <si>
     <t xml:space="preserve">Sweden</t>
   </si>
   <si>
-    <t xml:space="preserve">Victoria Carl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jessie Diggins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USA</t>
+    <t xml:space="preserve">Astrid Øyre Slind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ebba Andersson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pia Fink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Katerina Janatova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czechia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kristin Austgulen Fosnæs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moa Ilar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silje Theodorsen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helene Marie Fossesholm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kerttu Niskanen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nora Sanness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flora Dolci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emma Ribom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sophia Laukli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julia Kern</t>
   </si>
   <si>
     <t xml:space="preserve">Katharina Hennig</t>
   </si>
   <si>
-    <t xml:space="preserve">Therese Johaug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Norway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heidi Weng</t>
+    <t xml:space="preserve">Lotta Udnes Weng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teresa Stadlober</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johanna Hagström</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helen Hoffmann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julie Myhre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frida Karlsson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Märta Rosenberg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jasmin Kähärä</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sofie Krehl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Krista Pärmäkoski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Masae Tsuchiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Japan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mathilde Myhrvold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laura Gimmler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coletta Rydzek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hedda Østberg Amundsen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anna Comarella</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jasmi Joensuu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caterina Ganz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Katri Lylynperä</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liliane Gagnon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delphine Claudel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moa Lundgren</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elena Rise Johnsen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingrid Bergene Aabrekk</t>
   </si>
   <si>
     <t xml:space="preserve">Rosie Brennan</t>
   </si>
   <si>
-    <t xml:space="preserve">Frida Karlsson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ebba Andersson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linn Svahn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teresa Stadlober</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Austria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kristin Austgulen Fosnæs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maja Dahlqvist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jasmi Joensuu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Astrid Øyre Slind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lotta Udnes Weng</t>
+    <t xml:space="preserve">Katharina Brudermann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lena Quintin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alayna Sonnesyn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Katherine Sauerbrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nadja Kälin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switzerland</t>
   </si>
   <si>
     <t xml:space="preserve">Anne Kyllönen</t>
   </si>
   <si>
-    <t xml:space="preserve">Laura Gimmler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kerttu Niskanen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Johanna Hagström</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Johanna Matintalo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pia Fink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Katri Lylynperä</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Julie Myhre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Krista Pärmäkoski</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Katerina Janatova</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czechia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coletta Rydzek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nadine Fähndrich</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Switzerland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sophia Laukli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emma Ribom</t>
+    <t xml:space="preserve">Kaidy Kaasiku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chika Kobayashi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berit Mogstad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Izabela Marcisz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hilla Niemela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mali Eidnes Bakken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ane Appelkvist Stenseth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eva Ingebrigtsen</t>
   </si>
   <si>
     <t xml:space="preserve">Anja Weber</t>
   </si>
   <si>
-    <t xml:space="preserve">Caterina Ganz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Italy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flora Dolci</t>
-  </si>
-  <si>
-    <t xml:space="preserve">France</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silje Theodorsen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nora Sanness</t>
+    <t xml:space="preserve">Amalie Håkonsen Ous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kathrine Stewart-Jones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keidy Kaasiku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kristine Stavås Skistad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicole Monsorno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maria Hartz Melling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosie Fordham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Australia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eva Urevc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slovenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juliette Ducordeau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marte Skaanes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiril Udnes Weng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anniken Sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francesca Franchi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hanne Wilberg Rofstad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johanne Hauge Harviken</t>
   </si>
   <si>
     <t xml:space="preserve">Amanda Saari</t>
   </si>
   <si>
-    <t xml:space="preserve">Katherine Sauerbrey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sofie Krehl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Märta Rosenberg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiril Udnes Weng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nicole Monsorno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delphine Claudel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moa Ilar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ane Appelkvist Stenseth</t>
+    <t xml:space="preserve">Barbora Havlickova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuva Anine Brusveen-Jensen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lauren Jortberg</t>
   </si>
   <si>
     <t xml:space="preserve">Vilma Nissinen</t>
   </si>
   <si>
-    <t xml:space="preserve">Nadja Kälin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hedda Østberg Amundsen</t>
+    <t xml:space="preserve">Desiree Steiner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisa Eriksson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darya Ryazhko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kazakhstan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evelina Crusell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lena Keck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teesi Tuul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erin Bianco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sydney Palmer-Leger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kseniya Shalygina</t>
   </si>
   <si>
     <t xml:space="preserve">Barbora Antosova</t>
   </si>
   <si>
-    <t xml:space="preserve">Helen Hoffmann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jasmin Kähärä</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Julia Kern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kathrine Stewart-Jones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liliane Gagnon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alayna Sonnesyn</t>
+    <t xml:space="preserve">Kamila Makhmutova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Da-Som Han</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Korea</t>
   </si>
   <si>
     <t xml:space="preserve">Melissa Gal</t>
   </si>
   <si>
-    <t xml:space="preserve">Lena Quintin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiia Olkkonen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anna Comarella</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nora Kytäjä</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desiree Steiner</t>
+    <t xml:space="preserve">Angelina Shuryga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anja Mandeljc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chika Honda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ellen Søhol Lie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eui Jin Lee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haley Brewster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kitija Auzina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latvia</t>
   </si>
   <si>
     <t xml:space="preserve">Lisa Lohmann</t>
   </si>
   <si>
-    <t xml:space="preserve">Anja Mandeljc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slovenia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sydney Palmer-Leger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barbora Havlickova</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eva Urevc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anni Alakoski</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ella Noora Haapalehto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eveliina Piippo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oona Kettunen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haley Brewster</t>
+    <t xml:space="preserve">Maelle Veyre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nadezhda Stepashkina</t>
   </si>
   <si>
     <t xml:space="preserve">Renae Anderson</t>
   </si>
   <si>
-    <t xml:space="preserve">Erin Bianco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emmi Lämsä</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teesi Tuul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juliette Ducordeau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nadezhda Stepashkina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kazakhstan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lauren Jortberg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maelle Veyre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Darya Ryazhko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rebecca Immonen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Francesca Franchi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kseniya Shalygina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anastasiia Nikon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ukraine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angelina Shuryga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elsa Torvinen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frida Haggkvist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kamila Makhmutova</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Katya Galstyan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armenia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitija Auzina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latvia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosie Fordham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Australia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viktoriya Olekh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yelizaveta Nopriienko</t>
+    <t xml:space="preserve">Sonjaa Schmidt</t>
   </si>
 </sst>
 </file>
@@ -728,22 +770,22 @@
         <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>1725.46354647902</v>
+        <v>1695.80733967663</v>
       </c>
       <c r="D2" t="n">
-        <v>1786.7216593634</v>
+        <v>1780.61162723371</v>
       </c>
       <c r="E2" t="n">
-        <v>61.2581128843742</v>
+        <v>84.8042875570873</v>
       </c>
       <c r="F2" t="n">
-        <v>157.474131621738</v>
+        <v>245.509296951538</v>
       </c>
       <c r="G2" t="n">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="H2" t="n">
-        <v>76.525868378262</v>
+        <v>-6.509296951538</v>
       </c>
     </row>
     <row r="3">
@@ -754,22 +796,22 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>1599.87431406729</v>
+        <v>1695.1828998355</v>
       </c>
       <c r="D3" t="n">
-        <v>1695.1828998355</v>
+        <v>1763.68295919247</v>
       </c>
       <c r="E3" t="n">
-        <v>95.3085857682113</v>
+        <v>68.5000593569675</v>
       </c>
       <c r="F3" t="n">
         <v>185.492395529462</v>
       </c>
       <c r="G3" t="n">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="H3" t="n">
-        <v>12.507604470538</v>
+        <v>37.507604470538</v>
       </c>
     </row>
     <row r="4">
@@ -780,22 +822,22 @@
         <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>1680.19589485824</v>
+        <v>1846.90906113836</v>
       </c>
       <c r="D4" t="n">
-        <v>1695.80733967663</v>
+        <v>1902.2931248352</v>
       </c>
       <c r="E4" t="n">
-        <v>15.6114448183848</v>
+        <v>55.3840636968396</v>
       </c>
       <c r="F4" t="n">
-        <v>245.509296951538</v>
+        <v>186.795438770195</v>
       </c>
       <c r="G4" t="n">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="H4" t="n">
-        <v>-49.509296951538</v>
+        <v>13.204561229805</v>
       </c>
     </row>
     <row r="5">
@@ -803,25 +845,25 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
-        <v>1582.60556376585</v>
+        <v>1737.82205140848</v>
       </c>
       <c r="D5" t="n">
-        <v>1658.7660661937</v>
+        <v>1816.69762601102</v>
       </c>
       <c r="E5" t="n">
-        <v>76.1605024278517</v>
+        <v>78.8755746025352</v>
       </c>
       <c r="F5" t="n">
-        <v>147.12763504316</v>
+        <v>158.836231015093</v>
       </c>
       <c r="G5" t="n">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="H5" t="n">
-        <v>46.87236495684</v>
+        <v>31.163768984907</v>
       </c>
     </row>
     <row r="6">
@@ -832,22 +874,22 @@
         <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>1798.22701302938</v>
+        <v>1786.7216593634</v>
       </c>
       <c r="D6" t="n">
-        <v>1846.90906113836</v>
+        <v>1830.71231835823</v>
       </c>
       <c r="E6" t="n">
-        <v>48.6820481089837</v>
+        <v>43.9906589948321</v>
       </c>
       <c r="F6" t="n">
-        <v>186.795438770195</v>
+        <v>157.474131621738</v>
       </c>
       <c r="G6" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="H6" t="n">
-        <v>-6.79543877019501</v>
+        <v>17.525868378262</v>
       </c>
     </row>
     <row r="7">
@@ -855,25 +897,25 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>1632.85042396796</v>
+        <v>1612.44651733859</v>
       </c>
       <c r="D7" t="n">
-        <v>1737.82205140848</v>
+        <v>1721.98964017595</v>
       </c>
       <c r="E7" t="n">
-        <v>104.971627440525</v>
+        <v>109.543122837357</v>
       </c>
       <c r="F7" t="n">
-        <v>158.836231015093</v>
+        <v>114.864033343141</v>
       </c>
       <c r="G7" t="n">
         <v>170</v>
       </c>
       <c r="H7" t="n">
-        <v>11.163768984907</v>
+        <v>55.135966656859</v>
       </c>
     </row>
     <row r="8">
@@ -881,25 +923,25 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>1599.49032825509</v>
+        <v>1719.40557037788</v>
       </c>
       <c r="D8" t="n">
-        <v>1610.68050185189</v>
+        <v>1774.39291461042</v>
       </c>
       <c r="E8" t="n">
-        <v>11.1901735968065</v>
+        <v>54.9873442325409</v>
       </c>
       <c r="F8" t="n">
-        <v>149.143504982219</v>
+        <v>148.513428478032</v>
       </c>
       <c r="G8" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H8" t="n">
-        <v>8.85649501778099</v>
+        <v>8.48657152196799</v>
       </c>
     </row>
     <row r="9">
@@ -907,25 +949,25 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>1682.84006889543</v>
+        <v>1545.83656689025</v>
       </c>
       <c r="D9" t="n">
-        <v>1704.10016178902</v>
+        <v>1590.28710761097</v>
       </c>
       <c r="E9" t="n">
-        <v>21.2600928935981</v>
+        <v>44.4505407207223</v>
       </c>
       <c r="F9" t="n">
-        <v>150.117000770042</v>
+        <v>113.001306631739</v>
       </c>
       <c r="G9" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.11700077004201</v>
+        <v>38.998693368261</v>
       </c>
     </row>
     <row r="10">
@@ -933,77 +975,77 @@
         <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>1660.88903794955</v>
+        <v>1470.55609745366</v>
       </c>
       <c r="D10" t="n">
-        <v>1719.40557037788</v>
+        <v>1527.49503893647</v>
       </c>
       <c r="E10" t="n">
-        <v>58.5165324283278</v>
+        <v>56.9389414828076</v>
       </c>
       <c r="F10" t="n">
-        <v>148.513428478032</v>
+        <v>116.795056006933</v>
       </c>
       <c r="G10" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H10" t="n">
-        <v>-7.51342847803201</v>
+        <v>26.204943993067</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>1682.60660191296</v>
+        <v>1527.42966774298</v>
       </c>
       <c r="D11" t="n">
-        <v>1619.17253949453</v>
+        <v>1630.71961712471</v>
       </c>
       <c r="E11" t="n">
-        <v>-63.4340624184345</v>
+        <v>103.289949381726</v>
       </c>
       <c r="F11" t="n">
-        <v>152.058336236276</v>
+        <v>91.5906622054468</v>
       </c>
       <c r="G11" t="n">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="H11" t="n">
-        <v>-11.058336236276</v>
+        <v>37.4093377945532</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>1541.60284997123</v>
+        <v>1530.30788154536</v>
       </c>
       <c r="D12" t="n">
-        <v>1660.25565408478</v>
+        <v>1524.08721384142</v>
       </c>
       <c r="E12" t="n">
-        <v>118.652804113552</v>
+        <v>-6.22066770394281</v>
       </c>
       <c r="F12" t="n">
-        <v>140.713886247231</v>
+        <v>81.0817878832061</v>
       </c>
       <c r="G12" t="n">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="H12" t="n">
-        <v>0.286113752769012</v>
+        <v>42.9182121167939</v>
       </c>
     </row>
     <row r="13">
@@ -1011,25 +1053,25 @@
         <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>1420.74953524365</v>
+        <v>1506.88798257664</v>
       </c>
       <c r="D13" t="n">
-        <v>1527.42966774298</v>
+        <v>1590.68328806405</v>
       </c>
       <c r="E13" t="n">
-        <v>106.680132499334</v>
+        <v>83.7953054874072</v>
       </c>
       <c r="F13" t="n">
-        <v>91.5906622054468</v>
+        <v>83.3130048500462</v>
       </c>
       <c r="G13" t="n">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="H13" t="n">
-        <v>42.4093377945532</v>
+        <v>37.6869951499538</v>
       </c>
     </row>
     <row r="14">
@@ -1037,25 +1079,25 @@
         <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>1552.39983009666</v>
+        <v>1480.63475673186</v>
       </c>
       <c r="D14" t="n">
-        <v>1611.44500599574</v>
+        <v>1575.61868680275</v>
       </c>
       <c r="E14" t="n">
-        <v>59.0451758990762</v>
+        <v>94.983930070897</v>
       </c>
       <c r="F14" t="n">
-        <v>98.5314322927071</v>
+        <v>94.1824293476958</v>
       </c>
       <c r="G14" t="n">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="H14" t="n">
-        <v>35.4685677072929</v>
+        <v>22.8175706523042</v>
       </c>
     </row>
     <row r="15">
@@ -1066,22 +1108,22 @@
         <v>27</v>
       </c>
       <c r="C15" t="n">
-        <v>1492.34040989161</v>
+        <v>1526.99006946935</v>
       </c>
       <c r="D15" t="n">
-        <v>1619.16005393289</v>
+        <v>1512.12468948335</v>
       </c>
       <c r="E15" t="n">
-        <v>126.81964404128</v>
+        <v>-14.8653799859974</v>
       </c>
       <c r="F15" t="n">
-        <v>86.9323904117037</v>
+        <v>59.2001477247346</v>
       </c>
       <c r="G15" t="n">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="H15" t="n">
-        <v>45.0676095882963</v>
+        <v>55.7998522752654</v>
       </c>
     </row>
     <row r="16">
@@ -1089,25 +1131,25 @@
         <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>1579.26803021557</v>
+        <v>1453.55718439061</v>
       </c>
       <c r="D16" t="n">
-        <v>1612.44651733859</v>
+        <v>1566.90936055826</v>
       </c>
       <c r="E16" t="n">
-        <v>33.1784871230188</v>
+        <v>113.352176167649</v>
       </c>
       <c r="F16" t="n">
-        <v>114.864033343141</v>
+        <v>78.2672487700003</v>
       </c>
       <c r="G16" t="n">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="H16" t="n">
-        <v>9.135966656859</v>
+        <v>35.7327512299997</v>
       </c>
     </row>
     <row r="17">
@@ -1115,347 +1157,363 @@
         <v>29</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C17" t="n">
-        <v>1482.8301927214</v>
+        <v>1489.7440957789</v>
       </c>
       <c r="D17" t="n">
-        <v>1532.52952616121</v>
+        <v>1469.67441311283</v>
       </c>
       <c r="E17" t="n">
-        <v>49.6993334398073</v>
+        <v>-20.0696826660758</v>
       </c>
       <c r="F17" t="n">
-        <v>92.2158598966909</v>
+        <v>92.9716404106692</v>
       </c>
       <c r="G17" t="n">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="H17" t="n">
-        <v>31.7841401033091</v>
+        <v>20.0283595893308</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>1394.86641886793</v>
+        <v>1553.49992496691</v>
       </c>
       <c r="D18" t="n">
-        <v>1448.02315016282</v>
+        <v>1577.48546018717</v>
       </c>
       <c r="E18" t="n">
-        <v>53.1567312948921</v>
+        <v>23.9855352202669</v>
       </c>
       <c r="F18" t="n">
-        <v>8.78618402087954</v>
+        <v>131.790316038262</v>
       </c>
       <c r="G18" t="n">
         <v>112</v>
       </c>
       <c r="H18" t="n">
-        <v>103.21381597912</v>
+        <v>-19.790316038262</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>1509.30377649462</v>
+        <v>1524.50882214323</v>
       </c>
       <c r="D19" t="n">
-        <v>1587.54552838174</v>
+        <v>1600.62602194328</v>
       </c>
       <c r="E19" t="n">
-        <v>78.2417518871191</v>
-      </c>
-      <c r="F19"/>
+        <v>76.1171998000534</v>
+      </c>
+      <c r="F19" t="n">
+        <v>89.0967705580833</v>
+      </c>
       <c r="G19" t="n">
-        <v>107</v>
-      </c>
-      <c r="H19"/>
+        <v>112</v>
+      </c>
+      <c r="H19" t="n">
+        <v>22.9032294419167</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>1628.93183054361</v>
+        <v>1335.77829411255</v>
       </c>
       <c r="D20" t="n">
-        <v>1526.99006946935</v>
+        <v>1459.36421399428</v>
       </c>
       <c r="E20" t="n">
-        <v>-101.941761074267</v>
+        <v>123.585919881731</v>
       </c>
       <c r="F20" t="n">
-        <v>59.2001477247346</v>
+        <v>89.3199939828106</v>
       </c>
       <c r="G20" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H20" t="n">
-        <v>44.7998522752654</v>
+        <v>17.6800060171894</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C21" t="n">
-        <v>1520.60209709921</v>
+        <v>1658.7660661937</v>
       </c>
       <c r="D21" t="n">
-        <v>1618.72652621752</v>
+        <v>1643.31850165287</v>
       </c>
       <c r="E21" t="n">
-        <v>98.1244291183166</v>
+        <v>-15.4475645408315</v>
       </c>
       <c r="F21" t="n">
-        <v>93.8076600913176</v>
+        <v>147.12763504316</v>
       </c>
       <c r="G21" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H21" t="n">
-        <v>6.1923399086824</v>
+        <v>-49.12763504316</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C22" t="n">
-        <v>1534.20866494398</v>
+        <v>1532.52952616121</v>
       </c>
       <c r="D22" t="n">
-        <v>1583.11080142478</v>
+        <v>1566.03634245618</v>
       </c>
       <c r="E22" t="n">
-        <v>48.9021364807952</v>
-      </c>
-      <c r="F22"/>
+        <v>33.5068162949667</v>
+      </c>
+      <c r="F22" t="n">
+        <v>92.2158598966909</v>
+      </c>
       <c r="G22" t="n">
         <v>98</v>
       </c>
-      <c r="H22"/>
+      <c r="H22" t="n">
+        <v>5.7841401033091</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="C23" t="n">
-        <v>1444.05293753101</v>
+        <v>1660.25565408478</v>
       </c>
       <c r="D23" t="n">
-        <v>1545.83656689025</v>
+        <v>1639.48478943731</v>
       </c>
       <c r="E23" t="n">
-        <v>101.783629359241</v>
+        <v>-20.7708646474691</v>
       </c>
       <c r="F23" t="n">
-        <v>113.001306631739</v>
+        <v>140.713886247231</v>
       </c>
       <c r="G23" t="n">
         <v>98</v>
       </c>
       <c r="H23" t="n">
-        <v>-15.001306631739</v>
+        <v>-42.713886247231</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C24" t="n">
-        <v>1358.84675421209</v>
+        <v>1618.72652621752</v>
       </c>
       <c r="D24" t="n">
-        <v>1505.72584365508</v>
+        <v>1685.63549013122</v>
       </c>
       <c r="E24" t="n">
-        <v>146.879089442982</v>
+        <v>66.9089639136989</v>
       </c>
       <c r="F24" t="n">
-        <v>13.7690048385212</v>
+        <v>93.8076600913176</v>
       </c>
       <c r="G24" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H24" t="n">
-        <v>82.2309951614788</v>
+        <v>1.1923399086824</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C25" t="n">
-        <v>1462.74384005661</v>
+        <v>1373.53957500011</v>
       </c>
       <c r="D25" t="n">
-        <v>1574.0053147822</v>
+        <v>1492.5416599497</v>
       </c>
       <c r="E25" t="n">
-        <v>111.261474725588</v>
+        <v>119.002084949586</v>
       </c>
       <c r="F25" t="n">
-        <v>47.7848122491326</v>
+        <v>42.7610206604834</v>
       </c>
       <c r="G25" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H25" t="n">
-        <v>47.2151877508674</v>
+        <v>49.2389793395166</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C26" t="n">
-        <v>1570.77566449773</v>
+        <v>1574.0053147822</v>
       </c>
       <c r="D26" t="n">
-        <v>1579.52585855551</v>
+        <v>1648.68541234517</v>
       </c>
       <c r="E26" t="n">
-        <v>8.75019405777152</v>
+        <v>74.6800975629774</v>
       </c>
       <c r="F26" t="n">
-        <v>70.1407511505321</v>
+        <v>47.7848122491326</v>
       </c>
       <c r="G26" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H26" t="n">
-        <v>23.8592488494679</v>
+        <v>42.2151877508674</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B27" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="C27" t="n">
-        <v>1479.00714386911</v>
+        <v>1704.10016178902</v>
       </c>
       <c r="D27" t="n">
-        <v>1470.55609745366</v>
+        <v>1744.63512639428</v>
       </c>
       <c r="E27" t="n">
-        <v>-8.45104641544958</v>
+        <v>40.5349646052573</v>
       </c>
       <c r="F27" t="n">
-        <v>116.795056006933</v>
+        <v>150.117000770042</v>
       </c>
       <c r="G27" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="H27" t="n">
-        <v>-23.795056006933</v>
+        <v>-65.117000770042</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C28" t="n">
-        <v>1492.07098147782</v>
+        <v>1416.89423701599</v>
       </c>
       <c r="D28" t="n">
-        <v>1548.47328375548</v>
+        <v>1474.42757153315</v>
       </c>
       <c r="E28" t="n">
-        <v>56.402302277661</v>
-      </c>
-      <c r="F28"/>
+        <v>57.5333345171634</v>
+      </c>
+      <c r="F28" t="n">
+        <v>23.1769466009091</v>
+      </c>
       <c r="G28" t="n">
-        <v>92</v>
-      </c>
-      <c r="H28"/>
+        <v>74</v>
+      </c>
+      <c r="H28" t="n">
+        <v>50.8230533990909</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B29" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C29" t="n">
-        <v>1572.3146458684</v>
+        <v>1468.43730420632</v>
       </c>
       <c r="D29" t="n">
-        <v>1555.09577224995</v>
+        <v>1557.07494167776</v>
       </c>
       <c r="E29" t="n">
-        <v>-17.2188736184489</v>
-      </c>
-      <c r="F29"/>
+        <v>88.6376374714357</v>
+      </c>
+      <c r="F29" t="n">
+        <v>56.6096058179146</v>
+      </c>
       <c r="G29" t="n">
-        <v>88</v>
-      </c>
-      <c r="H29"/>
+        <v>72</v>
+      </c>
+      <c r="H29" t="n">
+        <v>15.3903941820854</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
         <v>44</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C30" t="n">
-        <v>1450.87024500942</v>
+        <v>1413.75312496512</v>
       </c>
       <c r="D30" t="n">
-        <v>1524.50882214323</v>
+        <v>1459.71868302448</v>
       </c>
       <c r="E30" t="n">
-        <v>73.63857713381</v>
+        <v>45.9655580593644</v>
       </c>
       <c r="F30" t="n">
-        <v>89.0967705580833</v>
+        <v>67.5791806095622</v>
       </c>
       <c r="G30" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="H30" t="n">
-        <v>-6.09677055808331</v>
+        <v>2.4208193904378</v>
       </c>
     </row>
     <row r="31">
@@ -1463,25 +1521,25 @@
         <v>45</v>
       </c>
       <c r="B31" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C31" t="n">
-        <v>1603.05215417912</v>
+        <v>1579.52585855551</v>
       </c>
       <c r="D31" t="n">
-        <v>1553.49992496691</v>
+        <v>1628.63230576694</v>
       </c>
       <c r="E31" t="n">
-        <v>-49.5522292122137</v>
+        <v>49.1064472114399</v>
       </c>
       <c r="F31" t="n">
-        <v>131.790316038262</v>
+        <v>70.1407511505321</v>
       </c>
       <c r="G31" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="H31" t="n">
-        <v>-53.790316038262</v>
+        <v>-1.1407511505321</v>
       </c>
     </row>
     <row r="32">
@@ -1489,47 +1547,51 @@
         <v>46</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C32" t="n">
-        <v>1354.73363968207</v>
+        <v>1301.72977331064</v>
       </c>
       <c r="D32" t="n">
-        <v>1373.1225545835</v>
+        <v>1395.75020523322</v>
       </c>
       <c r="E32" t="n">
-        <v>18.3889149014306</v>
-      </c>
-      <c r="F32"/>
+        <v>94.0204319225807</v>
+      </c>
+      <c r="F32" t="n">
+        <v>23.5812842813713</v>
+      </c>
       <c r="G32" t="n">
-        <v>75</v>
-      </c>
-      <c r="H32"/>
+        <v>68</v>
+      </c>
+      <c r="H32" t="n">
+        <v>44.4187157186287</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B33" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="C33" t="n">
-        <v>1389.60354003924</v>
+        <v>1485.27636891609</v>
       </c>
       <c r="D33" t="n">
-        <v>1474.83710333112</v>
+        <v>1558.20875500487</v>
       </c>
       <c r="E33" t="n">
-        <v>85.2335632918764</v>
+        <v>72.932386088786</v>
       </c>
       <c r="F33" t="n">
-        <v>72.9394750503483</v>
+        <v>66.2369720445337</v>
       </c>
       <c r="G33" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="H33" t="n">
-        <v>1.06052494965169</v>
+        <v>-0.236972044533701</v>
       </c>
     </row>
     <row r="34">
@@ -1537,103 +1599,95 @@
         <v>49</v>
       </c>
       <c r="B34" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="C34" t="n">
-        <v>1427.80321676098</v>
+        <v>1587.54552838174</v>
       </c>
       <c r="D34" t="n">
-        <v>1489.7440957789</v>
+        <v>1512.67289670922</v>
       </c>
       <c r="E34" t="n">
-        <v>61.9408790179257</v>
-      </c>
-      <c r="F34" t="n">
-        <v>92.9716404106692</v>
-      </c>
+        <v>-74.8726316725235</v>
+      </c>
+      <c r="F34"/>
       <c r="G34" t="n">
-        <v>74</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-18.9716404106692</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="H34"/>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B35" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C35" t="n">
-        <v>1464.76883230134</v>
+        <v>1548.47328375548</v>
       </c>
       <c r="D35" t="n">
-        <v>1506.88798257664</v>
+        <v>1595.92193377655</v>
       </c>
       <c r="E35" t="n">
-        <v>42.119150275304</v>
-      </c>
-      <c r="F35" t="n">
-        <v>83.3130048500462</v>
-      </c>
+        <v>47.4486500210735</v>
+      </c>
+      <c r="F35"/>
       <c r="G35" t="n">
-        <v>73</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-10.3130048500462</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="H35"/>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B36" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C36" t="n">
-        <v>1324.37138091709</v>
+        <v>1448.967401026</v>
       </c>
       <c r="D36" t="n">
-        <v>1453.55718439061</v>
+        <v>1524.30133088241</v>
       </c>
       <c r="E36" t="n">
-        <v>129.185803473517</v>
+        <v>75.3339298564065</v>
       </c>
       <c r="F36" t="n">
-        <v>78.2672487700003</v>
+        <v>27.6934823290175</v>
       </c>
       <c r="G36" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H36" t="n">
-        <v>-9.26724877000029</v>
+        <v>32.3065176709825</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37" t="s">
         <v>53</v>
       </c>
-      <c r="B37" t="s">
-        <v>27</v>
-      </c>
       <c r="C37" t="n">
-        <v>1307.00529333087</v>
+        <v>1291.7365827815</v>
       </c>
       <c r="D37" t="n">
-        <v>1433.85619036117</v>
+        <v>1378.93563857936</v>
       </c>
       <c r="E37" t="n">
-        <v>126.850897030302</v>
+        <v>87.1990557978575</v>
       </c>
       <c r="F37" t="n">
-        <v>2.24887845958402</v>
+        <v>22.9223067001553</v>
       </c>
       <c r="G37" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="H37" t="n">
-        <v>63.751121540416</v>
+        <v>34.0776932998447</v>
       </c>
     </row>
     <row r="38">
@@ -1641,47 +1695,51 @@
         <v>54</v>
       </c>
       <c r="B38" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C38" t="n">
-        <v>1388.59316416661</v>
+        <v>1619.16005393289</v>
       </c>
       <c r="D38" t="n">
-        <v>1441.28313013066</v>
+        <v>1630.95077092151</v>
       </c>
       <c r="E38" t="n">
-        <v>52.6899659640483</v>
-      </c>
-      <c r="F38"/>
+        <v>11.7907169886255</v>
+      </c>
+      <c r="F38" t="n">
+        <v>86.9323904117037</v>
+      </c>
       <c r="G38" t="n">
-        <v>66</v>
-      </c>
-      <c r="H38"/>
+        <v>56</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-30.9323904117037</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
         <v>55</v>
       </c>
       <c r="B39" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="C39" t="n">
-        <v>1394.67436393834</v>
+        <v>1474.83710333112</v>
       </c>
       <c r="D39" t="n">
-        <v>1413.75312496512</v>
+        <v>1446.90792316844</v>
       </c>
       <c r="E39" t="n">
-        <v>19.0787610267812</v>
+        <v>-27.9291801626816</v>
       </c>
       <c r="F39" t="n">
-        <v>67.5791806095622</v>
+        <v>72.9394750503483</v>
       </c>
       <c r="G39" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="H39" t="n">
-        <v>-4.5791806095622</v>
+        <v>-18.9394750503483</v>
       </c>
     </row>
     <row r="40">
@@ -1689,25 +1747,25 @@
         <v>56</v>
       </c>
       <c r="B40" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C40" t="n">
-        <v>1337.75392349829</v>
+        <v>1505.72584365508</v>
       </c>
       <c r="D40" t="n">
-        <v>1416.89423701599</v>
+        <v>1546.856332486</v>
       </c>
       <c r="E40" t="n">
-        <v>79.1403135177009</v>
+        <v>41.1304888309282</v>
       </c>
       <c r="F40" t="n">
-        <v>23.1769466009091</v>
+        <v>13.7690048385212</v>
       </c>
       <c r="G40" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="H40" t="n">
-        <v>38.8230533990909</v>
+        <v>40.2309951614788</v>
       </c>
     </row>
     <row r="41">
@@ -1715,1231 +1773,1247 @@
         <v>57</v>
       </c>
       <c r="B41" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="C41" t="n">
-        <v>1529.07649656239</v>
+        <v>1308.17047722807</v>
       </c>
       <c r="D41" t="n">
-        <v>1490.90909942574</v>
+        <v>1320.36844710283</v>
       </c>
       <c r="E41" t="n">
-        <v>-38.167397136654</v>
+        <v>12.1979698747552</v>
       </c>
       <c r="F41" t="n">
-        <v>93.0656582548945</v>
+        <v>47.8483747207652</v>
       </c>
       <c r="G41" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H41" t="n">
-        <v>-35.0656582548945</v>
+        <v>5.1516252792348</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B42" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="C42" t="n">
-        <v>1366.885705039</v>
+        <v>1458.76509548586</v>
       </c>
       <c r="D42" t="n">
-        <v>1449.4217678841</v>
+        <v>1439.96454124711</v>
       </c>
       <c r="E42" t="n">
-        <v>82.5360628451044</v>
+        <v>-18.8005542387505</v>
       </c>
       <c r="F42" t="n">
-        <v>42.9136327807177</v>
+        <v>102.593747444924</v>
       </c>
       <c r="G42" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H42" t="n">
-        <v>11.0863672192823</v>
+        <v>-50.593747444924</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B43" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="C43" t="n">
-        <v>1494.12056735814</v>
+        <v>1471.40163320867</v>
       </c>
       <c r="D43" t="n">
-        <v>1458.76509548586</v>
+        <v>1519.02870952767</v>
       </c>
       <c r="E43" t="n">
-        <v>-35.3554718722773</v>
+        <v>47.6270763189993</v>
       </c>
       <c r="F43" t="n">
-        <v>102.593747444924</v>
+        <v>49.1289144045885</v>
       </c>
       <c r="G43" t="n">
         <v>52</v>
       </c>
       <c r="H43" t="n">
-        <v>-50.593747444924</v>
+        <v>2.8710855954115</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B44" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C44" t="n">
-        <v>1496.54816405952</v>
+        <v>1308.99719850566</v>
       </c>
       <c r="D44" t="n">
-        <v>1530.30788154536</v>
+        <v>1408.72305776001</v>
       </c>
       <c r="E44" t="n">
-        <v>33.7597174858399</v>
+        <v>99.7258592543485</v>
       </c>
       <c r="F44" t="n">
-        <v>81.0817878832061</v>
+        <v>15.735369533304</v>
       </c>
       <c r="G44" t="n">
         <v>50</v>
       </c>
       <c r="H44" t="n">
-        <v>-31.0817878832061</v>
+        <v>34.264630466696</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
-        <v>1441.42091908259</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C45"/>
       <c r="D45" t="n">
-        <v>1484.56760473171</v>
-      </c>
-      <c r="E45" t="n">
-        <v>43.146685649122</v>
-      </c>
+        <v>1392.86286005478</v>
+      </c>
+      <c r="E45"/>
       <c r="F45" t="n">
-        <v>39.1878979086848</v>
+        <v>0.518219198616987</v>
       </c>
       <c r="G45" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H45" t="n">
-        <v>8.8121020913152</v>
+        <v>45.481780801383</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B46" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="C46" t="n">
-        <v>1280.50776424832</v>
+        <v>1610.68050185189</v>
       </c>
       <c r="D46" t="n">
-        <v>1351.41473144935</v>
+        <v>1495.60158049003</v>
       </c>
       <c r="E46" t="n">
-        <v>70.9069672010341</v>
+        <v>-115.07892136186</v>
       </c>
       <c r="F46" t="n">
-        <v>15.0096826602974</v>
+        <v>149.143504982219</v>
       </c>
       <c r="G46" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H46" t="n">
-        <v>31.9903173397026</v>
+        <v>-105.143504982219</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B47" t="s">
-        <v>43</v>
-      </c>
-      <c r="C47" t="n">
-        <v>1341.67033115433</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="C47"/>
       <c r="D47" t="n">
-        <v>1315.88361021437</v>
-      </c>
-      <c r="E47" t="n">
-        <v>-25.7867209399533</v>
-      </c>
-      <c r="F47" t="n">
-        <v>35.2356888681742</v>
-      </c>
+        <v>1305.89427960949</v>
+      </c>
+      <c r="E47"/>
+      <c r="F47"/>
       <c r="G47" t="n">
-        <v>45</v>
-      </c>
-      <c r="H47" t="n">
-        <v>9.7643111318258</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="H47"/>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B48" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C48" t="n">
-        <v>1418.27320936447</v>
+        <v>1304.21026563896</v>
       </c>
       <c r="D48" t="n">
-        <v>1448.967401026</v>
+        <v>1375.60718991078</v>
       </c>
       <c r="E48" t="n">
-        <v>30.6941916615376</v>
+        <v>71.3969242718181</v>
       </c>
       <c r="F48" t="n">
-        <v>27.6934823290175</v>
+        <v>59.8527380033635</v>
       </c>
       <c r="G48" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H48" t="n">
-        <v>12.3065176709825</v>
+        <v>-21.8527380033635</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B49" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C49" t="n">
-        <v>1317.69066283496</v>
+        <v>1242.38238785014</v>
       </c>
       <c r="D49" t="n">
-        <v>1376.14626159057</v>
+        <v>1238.14917522034</v>
       </c>
       <c r="E49" t="n">
-        <v>58.4555987556014</v>
+        <v>-4.23321262979812</v>
       </c>
       <c r="F49" t="n">
-        <v>22.7431730573026</v>
+        <v>14.2635373273686</v>
       </c>
       <c r="G49" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H49" t="n">
-        <v>15.2568269426974</v>
+        <v>22.7364626726314</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B50" t="s">
         <v>11</v>
       </c>
       <c r="C50" t="n">
-        <v>1309.63044190342</v>
+        <v>1441.28313013066</v>
       </c>
       <c r="D50" t="n">
-        <v>1373.53957500011</v>
+        <v>1452.25622672314</v>
       </c>
       <c r="E50" t="n">
-        <v>63.9091330966887</v>
-      </c>
-      <c r="F50" t="n">
-        <v>42.7610206604834</v>
-      </c>
+        <v>10.9730965924755</v>
+      </c>
+      <c r="F50"/>
       <c r="G50" t="n">
-        <v>38</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-4.7610206604834</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="H50"/>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B51" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="C51" t="n">
-        <v>1424.89562055318</v>
+        <v>1315.88361021437</v>
       </c>
       <c r="D51" t="n">
-        <v>1468.43730420632</v>
+        <v>1274.15151902075</v>
       </c>
       <c r="E51" t="n">
-        <v>43.541683653141</v>
+        <v>-41.7320911936274</v>
       </c>
       <c r="F51" t="n">
-        <v>56.6096058179146</v>
+        <v>35.2356888681742</v>
       </c>
       <c r="G51" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H51" t="n">
-        <v>-20.6096058179146</v>
+        <v>-0.235688868174201</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B52" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C52" t="n">
-        <v>1467.91866482034</v>
+        <v>1448.02315016282</v>
       </c>
       <c r="D52" t="n">
-        <v>1335.77829411255</v>
+        <v>1377.92009639185</v>
       </c>
       <c r="E52" t="n">
-        <v>-132.140370707791</v>
+        <v>-70.1030537709692</v>
       </c>
       <c r="F52" t="n">
-        <v>89.3199939828106</v>
+        <v>8.78618402087954</v>
       </c>
       <c r="G52" t="n">
         <v>34</v>
       </c>
       <c r="H52" t="n">
-        <v>-55.3199939828106</v>
+        <v>25.2138159791205</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B53" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C53" t="n">
-        <v>1319.8294911521</v>
+        <v>1264.11329825906</v>
       </c>
       <c r="D53" t="n">
-        <v>1281.55044469426</v>
+        <v>1263.60286788295</v>
       </c>
       <c r="E53" t="n">
-        <v>-38.2790464578457</v>
+        <v>-0.510430376116119</v>
       </c>
       <c r="F53" t="n">
-        <v>35.2503750050057</v>
+        <v>28.0769442263843</v>
       </c>
       <c r="G53" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H53" t="n">
-        <v>-2.2503750050057</v>
+        <v>5.9230557736157</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B54" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="C54" t="n">
-        <v>1268.64270795716</v>
+        <v>1223.2356578981</v>
       </c>
       <c r="D54" t="n">
-        <v>1308.17047722807</v>
+        <v>1179.80521365477</v>
       </c>
       <c r="E54" t="n">
-        <v>39.5277692709055</v>
+        <v>-43.430444243332</v>
       </c>
       <c r="F54" t="n">
-        <v>47.8483747207652</v>
+        <v>5.89729017353722</v>
       </c>
       <c r="G54" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H54" t="n">
-        <v>-16.8483747207652</v>
+        <v>27.1027098264628</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
       </c>
       <c r="C55" t="n">
-        <v>1199.94927181752</v>
+        <v>1287.81035179595</v>
       </c>
       <c r="D55" t="n">
-        <v>1242.38238785014</v>
+        <v>1366.32518605492</v>
       </c>
       <c r="E55" t="n">
-        <v>42.4331160326142</v>
-      </c>
-      <c r="F55" t="n">
-        <v>14.2635373273686</v>
-      </c>
+        <v>78.5148342589725</v>
+      </c>
+      <c r="F55"/>
       <c r="G55" t="n">
-        <v>30</v>
-      </c>
-      <c r="H55" t="n">
-        <v>15.7364626726314</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="H55"/>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B56" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="C56" t="n">
-        <v>1333.50440160189</v>
+        <v>1268.53891622358</v>
       </c>
       <c r="D56" t="n">
-        <v>1316.94922655259</v>
+        <v>1204.21485966606</v>
       </c>
       <c r="E56" t="n">
-        <v>-16.5551750493</v>
+        <v>-64.3240565575211</v>
       </c>
       <c r="F56" t="n">
-        <v>41.5263107485463</v>
+        <v>31.6364391606767</v>
       </c>
       <c r="G56" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H56" t="n">
-        <v>-12.5263107485463</v>
+        <v>0.363560839323299</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B57" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="C57" t="n">
-        <v>1378.62240811387</v>
+        <v>1309.0529989625</v>
       </c>
       <c r="D57" t="n">
-        <v>1304.21026563896</v>
+        <v>1358.75935283616</v>
       </c>
       <c r="E57" t="n">
-        <v>-74.4121424749133</v>
+        <v>49.7063538736534</v>
       </c>
       <c r="F57" t="n">
-        <v>59.8527380033635</v>
+        <v>5.49364630156819</v>
       </c>
       <c r="G57" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H57" t="n">
-        <v>-33.8527380033635</v>
+        <v>24.5063536984318</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B58" t="s">
-        <v>27</v>
-      </c>
-      <c r="C58" t="n">
-        <v>1286.85763083447</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C58"/>
       <c r="D58" t="n">
-        <v>1325.02582887995</v>
-      </c>
-      <c r="E58" t="n">
-        <v>38.1681980454848</v>
-      </c>
-      <c r="F58"/>
+        <v>1368.68996780693</v>
+      </c>
+      <c r="E58"/>
+      <c r="F58" t="n">
+        <v>5.79223348835038</v>
+      </c>
       <c r="G58" t="n">
-        <v>26</v>
-      </c>
-      <c r="H58"/>
+        <v>30</v>
+      </c>
+      <c r="H58" t="n">
+        <v>24.2077665116496</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B59" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="C59" t="n">
-        <v>1294.56790842632</v>
+        <v>1484.56760473171</v>
       </c>
       <c r="D59" t="n">
-        <v>1291.7365827815</v>
+        <v>1467.73833351978</v>
       </c>
       <c r="E59" t="n">
-        <v>-2.8313256448148</v>
+        <v>-16.8292712119255</v>
       </c>
       <c r="F59" t="n">
-        <v>22.9223067001553</v>
+        <v>39.1878979086848</v>
       </c>
       <c r="G59" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H59" t="n">
-        <v>2.0776932998447</v>
+        <v>-11.1878979086848</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B60" t="s">
-        <v>27</v>
-      </c>
-      <c r="C60" t="n">
-        <v>1291.1596903241</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C60"/>
       <c r="D60" t="n">
-        <v>1216.38075515958</v>
-      </c>
-      <c r="E60" t="n">
-        <v>-74.7789351645181</v>
-      </c>
-      <c r="F60"/>
+        <v>1329.0376987743</v>
+      </c>
+      <c r="E60"/>
+      <c r="F60" t="n">
+        <v>16.8397255133708</v>
+      </c>
       <c r="G60" t="n">
-        <v>24</v>
-      </c>
-      <c r="H60"/>
+        <v>28</v>
+      </c>
+      <c r="H60" t="n">
+        <v>11.1602744866292</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B61" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="C61" t="n">
-        <v>1401.67674579535</v>
+        <v>1373.1225545835</v>
       </c>
       <c r="D61" t="n">
-        <v>1319.26777568108</v>
+        <v>1299.26888775224</v>
       </c>
       <c r="E61" t="n">
-        <v>-82.40897011427</v>
-      </c>
-      <c r="F61" t="n">
-        <v>67.8295652044732</v>
-      </c>
+        <v>-73.8536668312586</v>
+      </c>
+      <c r="F61"/>
       <c r="G61" t="n">
-        <v>20</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-47.8295652044732</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="H61"/>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B62" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C62" t="n">
-        <v>1341.76391042217</v>
+        <v>1306.3338019445</v>
       </c>
       <c r="D62" t="n">
-        <v>1342.47802279012</v>
+        <v>1346.98997632561</v>
       </c>
       <c r="E62" t="n">
-        <v>0.714112367946882</v>
+        <v>40.6561743811087</v>
       </c>
       <c r="F62" t="n">
-        <v>20.1682130191176</v>
+        <v>17.4500676506468</v>
       </c>
       <c r="G62" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="H62" t="n">
-        <v>-1.1682130191176</v>
+        <v>8.5499323493532</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B63" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="C63" t="n">
-        <v>1245.43240384284</v>
+        <v>1281.55044469426</v>
       </c>
       <c r="D63" t="n">
-        <v>1243.35598855697</v>
+        <v>1267.20301151964</v>
       </c>
       <c r="E63" t="n">
-        <v>-2.07641528586851</v>
+        <v>-14.3474331746156</v>
       </c>
       <c r="F63" t="n">
-        <v>24.4422495390402</v>
+        <v>35.2503750050057</v>
       </c>
       <c r="G63" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H63" t="n">
-        <v>-6.4422495390402</v>
+        <v>-10.2503750050057</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B64" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="C64" t="n">
-        <v>1279.23048956772</v>
+        <v>1236.34715880268</v>
       </c>
       <c r="D64" t="n">
-        <v>1242.73765272396</v>
+        <v>1208.05032333511</v>
       </c>
       <c r="E64" t="n">
-        <v>-36.492836843767</v>
+        <v>-28.2968354675725</v>
       </c>
       <c r="F64" t="n">
-        <v>17.7630489253037</v>
+        <v>15.7280354357724</v>
       </c>
       <c r="G64" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H64" t="n">
-        <v>-1.7630489253037</v>
+        <v>7.2719645642276</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B65" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="C65" t="n">
-        <v>1238.22004134044</v>
+        <v>1625.47816078038</v>
       </c>
       <c r="D65" t="n">
-        <v>1217.07764216363</v>
+        <v>1550.55815011664</v>
       </c>
       <c r="E65" t="n">
-        <v>-21.1423991768106</v>
+        <v>-74.92001066374</v>
       </c>
       <c r="F65" t="n">
-        <v>2.4717871797178</v>
+        <v>100</v>
       </c>
       <c r="G65" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H65" t="n">
-        <v>11.5282128202822</v>
+        <v>-78</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B66" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="C66" t="n">
-        <v>1390.94753238926</v>
+        <v>1449.4217678841</v>
       </c>
       <c r="D66" t="n">
-        <v>1279.21547974613</v>
+        <v>1305.95157045872</v>
       </c>
       <c r="E66" t="n">
-        <v>-111.732052643131</v>
+        <v>-143.470197425384</v>
       </c>
       <c r="F66" t="n">
-        <v>71.6699901300489</v>
+        <v>42.9136327807177</v>
       </c>
       <c r="G66" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H66" t="n">
-        <v>-58.6699901300489</v>
+        <v>-23.9136327807177</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B67" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C67" t="n">
-        <v>1307.31473236735</v>
+        <v>1361.24055093956</v>
       </c>
       <c r="D67" t="n">
-        <v>1314.69567417209</v>
+        <v>1357.51890126648</v>
       </c>
       <c r="E67" t="n">
-        <v>7.38094180473445</v>
-      </c>
-      <c r="F67"/>
+        <v>-3.72164967307458</v>
+      </c>
+      <c r="F67" t="n">
+        <v>32.8573835121087</v>
+      </c>
       <c r="G67" t="n">
-        <v>12</v>
-      </c>
-      <c r="H67"/>
+        <v>18</v>
+      </c>
+      <c r="H67" t="n">
+        <v>-14.8573835121087</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B68" t="s">
-        <v>27</v>
-      </c>
-      <c r="C68"/>
+        <v>89</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1210.52446523419</v>
+      </c>
       <c r="D68" t="n">
-        <v>1279.0607085021</v>
-      </c>
-      <c r="E68"/>
-      <c r="F68"/>
+        <v>1278.65075303469</v>
+      </c>
+      <c r="E68" t="n">
+        <v>68.1262878004998</v>
+      </c>
+      <c r="F68" t="n">
+        <v>17.7077816886833</v>
+      </c>
       <c r="G68" t="n">
-        <v>12</v>
-      </c>
-      <c r="H68"/>
+        <v>18</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.292218311316699</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B69" t="s">
-        <v>27</v>
+        <v>91</v>
       </c>
       <c r="C69" t="n">
-        <v>1358.30920122982</v>
+        <v>1279.21547974613</v>
       </c>
       <c r="D69" t="n">
-        <v>1316.50730934766</v>
+        <v>1299.25523984973</v>
       </c>
       <c r="E69" t="n">
-        <v>-41.8018918821613</v>
-      </c>
-      <c r="F69"/>
+        <v>20.0397601036018</v>
+      </c>
+      <c r="F69" t="n">
+        <v>71.6699901300489</v>
+      </c>
       <c r="G69" t="n">
-        <v>11</v>
-      </c>
-      <c r="H69"/>
+        <v>17</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-54.6699901300489</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B70" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C70" t="n">
-        <v>1278.81140329611</v>
+        <v>1224.3404667783</v>
       </c>
       <c r="D70" t="n">
-        <v>1224.1272280909</v>
+        <v>1205.38111566308</v>
       </c>
       <c r="E70" t="n">
-        <v>-54.6841752052128</v>
-      </c>
-      <c r="F70"/>
+        <v>-18.9593511152195</v>
+      </c>
+      <c r="F70" t="n">
+        <v>8.23844061231891</v>
+      </c>
       <c r="G70" t="n">
-        <v>10</v>
-      </c>
-      <c r="H70"/>
+        <v>16</v>
+      </c>
+      <c r="H70" t="n">
+        <v>7.76155938768109</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
       </c>
       <c r="C71" t="n">
-        <v>1295.11694181425</v>
+        <v>1344.95922796293</v>
       </c>
       <c r="D71" t="n">
-        <v>1211.19953532927</v>
+        <v>1322.19813869606</v>
       </c>
       <c r="E71" t="n">
-        <v>-83.9174064849728</v>
-      </c>
-      <c r="F71" t="n">
-        <v>12.2201424435406</v>
-      </c>
+        <v>-22.7610892668736</v>
+      </c>
+      <c r="F71"/>
       <c r="G71" t="n">
-        <v>9</v>
-      </c>
-      <c r="H71" t="n">
-        <v>-3.2201424435406</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="H71"/>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
       </c>
       <c r="C72" t="n">
-        <v>1258.38808283834</v>
+        <v>1490.90909942574</v>
       </c>
       <c r="D72" t="n">
-        <v>1235.25754196807</v>
+        <v>1431.95326935208</v>
       </c>
       <c r="E72" t="n">
-        <v>-23.1305408702763</v>
+        <v>-58.9558300736583</v>
       </c>
       <c r="F72" t="n">
-        <v>15.6352678848397</v>
+        <v>93.0656582548945</v>
       </c>
       <c r="G72" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H72" t="n">
-        <v>-6.6352678848397</v>
+        <v>-77.0656582548945</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
       </c>
-      <c r="C73" t="n">
-        <v>1295.65073565891</v>
-      </c>
+      <c r="C73"/>
       <c r="D73" t="n">
-        <v>1256.07647747457</v>
-      </c>
-      <c r="E73" t="n">
-        <v>-39.5742581843492</v>
-      </c>
-      <c r="F73"/>
+        <v>1284.0376987743</v>
+      </c>
+      <c r="E73"/>
+      <c r="F73" t="n">
+        <v>16.8397255133708</v>
+      </c>
       <c r="G73" t="n">
-        <v>8</v>
-      </c>
-      <c r="H73"/>
+        <v>15</v>
+      </c>
+      <c r="H73" t="n">
+        <v>-1.8397255133708</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B74" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C74" t="n">
-        <v>1253.76515880436</v>
+        <v>1270.31402664065</v>
       </c>
       <c r="D74" t="n">
-        <v>1225.12558057868</v>
+        <v>1214.64498940143</v>
       </c>
       <c r="E74" t="n">
-        <v>-28.6395782256809</v>
-      </c>
-      <c r="F74"/>
+        <v>-55.6690372392261</v>
+      </c>
+      <c r="F74" t="n">
+        <v>34.0153261123936</v>
+      </c>
       <c r="G74" t="n">
-        <v>7</v>
-      </c>
-      <c r="H74"/>
+        <v>15</v>
+      </c>
+      <c r="H74" t="n">
+        <v>-19.0153261123936</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B75" t="s">
-        <v>94</v>
+        <v>13</v>
       </c>
       <c r="C75" t="n">
-        <v>1229.07559335674</v>
+        <v>1325.13929924133</v>
       </c>
       <c r="D75" t="n">
-        <v>1139.68016397949</v>
+        <v>1319.20022894204</v>
       </c>
       <c r="E75" t="n">
-        <v>-89.3954293772529</v>
+        <v>-5.93907029929005</v>
       </c>
       <c r="F75" t="n">
-        <v>4.8472519978825</v>
+        <v>29.8910072214502</v>
       </c>
       <c r="G75" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H75" t="n">
-        <v>1.1527480021175</v>
+        <v>-14.8910072214502</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B76" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="C76" t="n">
-        <v>1323.39846455451</v>
+        <v>1286.96624910053</v>
       </c>
       <c r="D76" t="n">
-        <v>1224.3404667783</v>
+        <v>1310.81416447032</v>
       </c>
       <c r="E76" t="n">
-        <v>-99.057997776207</v>
+        <v>23.8479153697901</v>
       </c>
       <c r="F76" t="n">
-        <v>8.23844061231891</v>
+        <v>17.0850603421783</v>
       </c>
       <c r="G76" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H76" t="n">
-        <v>-3.23844061231891</v>
+        <v>-2.0850603421783</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B77" t="s">
-        <v>97</v>
+        <v>27</v>
       </c>
       <c r="C77" t="n">
-        <v>1095.06651617888</v>
+        <v>1433.85619036117</v>
       </c>
       <c r="D77" t="n">
-        <v>1003.54926144084</v>
+        <v>1384.44864938992</v>
       </c>
       <c r="E77" t="n">
-        <v>-91.5172547380398</v>
+        <v>-49.4075409712584</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>2.24887845958402</v>
       </c>
       <c r="G77" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H77" t="n">
-        <v>4</v>
+        <v>11.751121540416</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B78" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C78" t="n">
-        <v>1234.28433043608</v>
+        <v>1217.07764216363</v>
       </c>
       <c r="D78" t="n">
-        <v>1188.27633504606</v>
+        <v>1185.70226359708</v>
       </c>
       <c r="E78" t="n">
-        <v>-46.0079953900267</v>
-      </c>
-      <c r="F78"/>
+        <v>-31.3753785665476</v>
+      </c>
+      <c r="F78" t="n">
+        <v>2.4717871797178</v>
+      </c>
       <c r="G78" t="n">
-        <v>3</v>
-      </c>
-      <c r="H78"/>
+        <v>14</v>
+      </c>
+      <c r="H78" t="n">
+        <v>11.5282128202822</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B79" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="C79" t="n">
-        <v>1286.88598698149</v>
+        <v>1283.44006713488</v>
       </c>
       <c r="D79" t="n">
-        <v>1167.22098421902</v>
+        <v>1293.6778003481</v>
       </c>
       <c r="E79" t="n">
-        <v>-119.665002762476</v>
+        <v>10.2377332132237</v>
       </c>
       <c r="F79" t="n">
-        <v>28.0953522490531</v>
+        <v>5.79223348835038</v>
       </c>
       <c r="G79" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H79" t="n">
-        <v>-25.0953522490531</v>
+        <v>6.20776651164962</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B80" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
       <c r="C80" t="n">
-        <v>1125.67826891703</v>
+        <v>1188.27633504606</v>
       </c>
       <c r="D80" t="n">
-        <v>1081.33726271848</v>
+        <v>1208.01592852512</v>
       </c>
       <c r="E80" t="n">
-        <v>-44.3410061985467</v>
-      </c>
-      <c r="F80" t="n">
-        <v>2.78361376651054</v>
-      </c>
+        <v>19.7395934790657</v>
+      </c>
+      <c r="F80"/>
       <c r="G80" t="n">
-        <v>2</v>
-      </c>
-      <c r="H80" t="n">
-        <v>-0.78361376651054</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="H80"/>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B81" t="s">
         <v>27</v>
       </c>
       <c r="C81" t="n">
-        <v>1248.21400041809</v>
+        <v>1351.41473144935</v>
       </c>
       <c r="D81" t="n">
-        <v>1196.25887404464</v>
+        <v>1324.58478978475</v>
       </c>
       <c r="E81" t="n">
-        <v>-51.9551263734456</v>
-      </c>
-      <c r="F81"/>
+        <v>-26.8299416645998</v>
+      </c>
+      <c r="F81" t="n">
+        <v>15.0096826602974</v>
+      </c>
       <c r="G81" t="n">
-        <v>2</v>
-      </c>
-      <c r="H81"/>
+        <v>10</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-5.0096826602974</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B82" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="C82" t="n">
-        <v>1320.55310009821</v>
+        <v>1319.26777568108</v>
       </c>
       <c r="D82" t="n">
-        <v>1270.31402664065</v>
+        <v>1199.73150297304</v>
       </c>
       <c r="E82" t="n">
-        <v>-50.2390734575606</v>
+        <v>-119.536272708034</v>
       </c>
       <c r="F82" t="n">
-        <v>34.0153261123936</v>
+        <v>67.8295652044732</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H82" t="n">
-        <v>-33.0153261123936</v>
+        <v>-60.8295652044732</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B83" t="s">
-        <v>97</v>
+        <v>16</v>
       </c>
       <c r="C83" t="n">
-        <v>1100.02067646569</v>
+        <v>1295.2030072717</v>
       </c>
       <c r="D83" t="n">
-        <v>1016.81600589164</v>
+        <v>1275.7948321582</v>
       </c>
       <c r="E83" t="n">
-        <v>-83.2046705740504</v>
+        <v>-19.4081751134947</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>11.1731609691909</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H83" t="n">
-        <v>1</v>
+        <v>-4.1731609691909</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B84" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C84" t="n">
-        <v>1214.95739040807</v>
+        <v>1081.33726271848</v>
       </c>
       <c r="D84" t="n">
-        <v>1053.36671319035</v>
+        <v>1071.79539583696</v>
       </c>
       <c r="E84" t="n">
-        <v>-161.590677217721</v>
-      </c>
-      <c r="F84"/>
+        <v>-9.54186688151799</v>
+      </c>
+      <c r="F84" t="n">
+        <v>2.78361376651054</v>
+      </c>
       <c r="G84" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84"/>
+        <v>6</v>
+      </c>
+      <c r="H84" t="n">
+        <v>3.21638623348946</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B85" t="s">
-        <v>97</v>
+        <v>16</v>
       </c>
       <c r="C85" t="n">
-        <v>1183.99572793481</v>
+        <v>1291.25089552575</v>
       </c>
       <c r="D85" t="n">
-        <v>1073.00033886899</v>
+        <v>1268.4066366134</v>
       </c>
       <c r="E85" t="n">
-        <v>-110.995389065813</v>
+        <v>-22.8442589123451</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>13.2556349138666</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>-7.2556349138666</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B86" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C86" t="n">
-        <v>1275.07338231089</v>
+        <v>1318.44352309927</v>
       </c>
       <c r="D86" t="n">
-        <v>1227.18574508344</v>
+        <v>1264.85942989642</v>
       </c>
       <c r="E86" t="n">
-        <v>-47.8876372274494</v>
+        <v>-53.584093202857</v>
       </c>
       <c r="F86"/>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H86"/>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B87" t="s">
-        <v>27</v>
-      </c>
-      <c r="C87"/>
+        <v>72</v>
+      </c>
+      <c r="C87" t="n">
+        <v>1139.68016397949</v>
+      </c>
       <c r="D87" t="n">
-        <v>1219.0607085021</v>
-      </c>
-      <c r="E87"/>
-      <c r="F87"/>
+        <v>1064.78159850064</v>
+      </c>
+      <c r="E87" t="n">
+        <v>-74.8985654788503</v>
+      </c>
+      <c r="F87" t="n">
+        <v>4.8472519978825</v>
+      </c>
       <c r="G87" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87"/>
+        <v>5</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.1527480021175</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B88" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
       <c r="C88" t="n">
-        <v>1182.77583043557</v>
+        <v>1256.07647747457</v>
       </c>
       <c r="D88" t="n">
-        <v>1097.49020881237</v>
+        <v>1218.96594390229</v>
       </c>
       <c r="E88" t="n">
-        <v>-85.2856216231953</v>
+        <v>-37.1105335722773</v>
       </c>
       <c r="F88"/>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H88"/>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B89" t="s">
-        <v>111</v>
+        <v>9</v>
       </c>
       <c r="C89" t="n">
-        <v>1134.40825091411</v>
+        <v>1242.73765272396</v>
       </c>
       <c r="D89" t="n">
-        <v>1014.46143485507</v>
+        <v>1228.77874414499</v>
       </c>
       <c r="E89" t="n">
-        <v>-119.946816059037</v>
-      </c>
-      <c r="F89"/>
+        <v>-13.958908578968</v>
+      </c>
+      <c r="F89" t="n">
+        <v>17.7630489253037</v>
+      </c>
       <c r="G89" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89"/>
+        <v>4</v>
+      </c>
+      <c r="H89" t="n">
+        <v>-13.7630489253037</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B90" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C90" t="n">
-        <v>1132.76851977954</v>
+        <v>1016.81600589164</v>
       </c>
       <c r="D90" t="n">
-        <v>1054.56910850175</v>
+        <v>965.285346382461</v>
       </c>
       <c r="E90" t="n">
-        <v>-78.199411277782</v>
+        <v>-51.5306595091831</v>
       </c>
       <c r="F90" t="n">
-        <v>2.84478872152134</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H90" t="n">
-        <v>-2.84478872152134</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
@@ -2947,66 +3021,404 @@
         <v>114</v>
       </c>
       <c r="B91" t="s">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="C91" t="n">
-        <v>1264.48241593776</v>
+        <v>1376.14626159057</v>
       </c>
       <c r="D91" t="n">
-        <v>1210.52446523419</v>
+        <v>1287.12707758674</v>
       </c>
       <c r="E91" t="n">
-        <v>-53.9579507035742</v>
+        <v>-89.0191840038285</v>
       </c>
       <c r="F91" t="n">
-        <v>17.7077816886833</v>
+        <v>22.7431730573026</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H91" t="n">
-        <v>-17.7077816886833</v>
+        <v>-20.7431730573026</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B92" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C92" t="n">
-        <v>1124.85555259206</v>
+        <v>1097.49020881237</v>
       </c>
       <c r="D92" t="n">
-        <v>1056.83253548909</v>
+        <v>1036.85078581455</v>
       </c>
       <c r="E92" t="n">
-        <v>-68.0230171029696</v>
+        <v>-60.6394229978202</v>
       </c>
       <c r="F92"/>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H92"/>
     </row>
     <row r="93">
       <c r="A93" t="s">
+        <v>116</v>
+      </c>
+      <c r="B93" t="s">
         <v>117</v>
       </c>
-      <c r="B93" t="s">
-        <v>105</v>
-      </c>
-      <c r="C93"/>
+      <c r="C93" t="n">
+        <v>1155.49719685802</v>
+      </c>
       <c r="D93" t="n">
-        <v>1073.67630339438</v>
-      </c>
-      <c r="E93"/>
+        <v>1037.31846110205</v>
+      </c>
+      <c r="E93" t="n">
+        <v>-118.178735755977</v>
+      </c>
       <c r="F93"/>
       <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>118</v>
+      </c>
+      <c r="B94" t="s">
+        <v>30</v>
+      </c>
+      <c r="C94" t="n">
+        <v>1316.94922655259</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1179.00657308154</v>
+      </c>
+      <c r="E94" t="n">
+        <v>-137.942653471053</v>
+      </c>
+      <c r="F94" t="n">
+        <v>41.5263107485463</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" t="n">
+        <v>-40.5263107485463</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>119</v>
+      </c>
+      <c r="B95" t="s">
+        <v>107</v>
+      </c>
+      <c r="C95" t="n">
+        <v>1073.00033886899</v>
+      </c>
+      <c r="D95" t="n">
+        <v>999.933119026147</v>
+      </c>
+      <c r="E95" t="n">
+        <v>-73.0672198428472</v>
+      </c>
+      <c r="F95" t="n">
         <v>0</v>
       </c>
-      <c r="H93"/>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>120</v>
+      </c>
+      <c r="B96" t="s">
+        <v>91</v>
+      </c>
+      <c r="C96" t="n">
+        <v>1243.35598855697</v>
+      </c>
+      <c r="D96" t="n">
+        <v>1199.16096928815</v>
+      </c>
+      <c r="E96" t="n">
+        <v>-44.1950192688166</v>
+      </c>
+      <c r="F96" t="n">
+        <v>24.4422495390402</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>-24.4422495390402</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>121</v>
+      </c>
+      <c r="B97" t="s">
+        <v>47</v>
+      </c>
+      <c r="C97" t="n">
+        <v>1276.82639730742</v>
+      </c>
+      <c r="D97" t="n">
+        <v>1127.91520091496</v>
+      </c>
+      <c r="E97" t="n">
+        <v>-148.911196392454</v>
+      </c>
+      <c r="F97" t="n">
+        <v>20.799327984127</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>-20.799327984127</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>122</v>
+      </c>
+      <c r="B98" t="s">
+        <v>89</v>
+      </c>
+      <c r="C98" t="n">
+        <v>1186.99757308843</v>
+      </c>
+      <c r="D98" t="n">
+        <v>1127.12959370352</v>
+      </c>
+      <c r="E98" t="n">
+        <v>-59.8679793849112</v>
+      </c>
+      <c r="F98"/>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>123</v>
+      </c>
+      <c r="B99" t="s">
+        <v>117</v>
+      </c>
+      <c r="C99" t="n">
+        <v>1161.41561898781</v>
+      </c>
+      <c r="D99" t="n">
+        <v>1066.97725036295</v>
+      </c>
+      <c r="E99" t="n">
+        <v>-94.4383686248595</v>
+      </c>
+      <c r="F99" t="n">
+        <v>6.44740189859168</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>-6.44740189859168</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>124</v>
+      </c>
+      <c r="B100" t="s">
+        <v>9</v>
+      </c>
+      <c r="C100" t="n">
+        <v>1211.19953532927</v>
+      </c>
+      <c r="D100" t="n">
+        <v>1129.62174848741</v>
+      </c>
+      <c r="E100" t="n">
+        <v>-81.5777868418618</v>
+      </c>
+      <c r="F100" t="n">
+        <v>12.2201424435406</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>-12.2201424435406</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>125</v>
+      </c>
+      <c r="B101" t="s">
+        <v>126</v>
+      </c>
+      <c r="C101" t="n">
+        <v>1054.56910850175</v>
+      </c>
+      <c r="D101" t="n">
+        <v>974.542778219085</v>
+      </c>
+      <c r="E101" t="n">
+        <v>-80.0263302826687</v>
+      </c>
+      <c r="F101" t="n">
+        <v>2.84478872152134</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>-2.84478872152134</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>127</v>
+      </c>
+      <c r="B102" t="s">
+        <v>11</v>
+      </c>
+      <c r="C102" t="n">
+        <v>1342.47802279012</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1269.22098184725</v>
+      </c>
+      <c r="E102" t="n">
+        <v>-73.2570409428631</v>
+      </c>
+      <c r="F102" t="n">
+        <v>20.1682130191176</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>-20.1682130191176</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>128</v>
+      </c>
+      <c r="B103" t="s">
+        <v>30</v>
+      </c>
+      <c r="C103" t="n">
+        <v>1167.22098421902</v>
+      </c>
+      <c r="D103" t="n">
+        <v>1062.88931409563</v>
+      </c>
+      <c r="E103" t="n">
+        <v>-104.33167012338</v>
+      </c>
+      <c r="F103" t="n">
+        <v>28.0953522490531</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>-28.0953522490531</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>129</v>
+      </c>
+      <c r="B104" t="s">
+        <v>107</v>
+      </c>
+      <c r="C104" t="n">
+        <v>1003.54926144084</v>
+      </c>
+      <c r="D104" t="n">
+        <v>1010.79622994373</v>
+      </c>
+      <c r="E104" t="n">
+        <v>7.24696850289479</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>130</v>
+      </c>
+      <c r="B105" t="s">
+        <v>9</v>
+      </c>
+      <c r="C105" t="n">
+        <v>1235.25754196807</v>
+      </c>
+      <c r="D105" t="n">
+        <v>1068.8491363883</v>
+      </c>
+      <c r="E105" t="n">
+        <v>-166.408405579767</v>
+      </c>
+      <c r="F105" t="n">
+        <v>15.6352678848397</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>-15.6352678848397</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>131</v>
+      </c>
+      <c r="B106" t="s">
+        <v>58</v>
+      </c>
+      <c r="C106" t="n">
+        <v>1258.12853429438</v>
+      </c>
+      <c r="D106" t="n">
+        <v>1193.25269526219</v>
+      </c>
+      <c r="E106" t="n">
+        <v>-64.8758390321852</v>
+      </c>
+      <c r="F106" t="n">
+        <v>35.1059824194583</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>-35.1059824194583</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
